--- a/data/Mörel-Filet/investment_decision/Mörel_MFH_until_2004_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Mörel_MFH_until_2004_investment_decision.xlsx
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>37.13764021657018</v>
+        <v>61.13348142599695</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>55775.116478856</v>
       </c>
       <c r="F2" t="n">
-        <v>37.13764021657018</v>
+        <v>61.13348142599695</v>
       </c>
       <c r="G2" t="n">
         <v>55775.116478856</v>
       </c>
       <c r="H2" t="n">
-        <v>37.13764021657018</v>
+        <v>61.13348142599695</v>
       </c>
       <c r="I2" t="n">
         <v>55775.116478856</v>
       </c>
       <c r="J2" t="n">
-        <v>37.13764021657018</v>
+        <v>61.13348142599695</v>
       </c>
       <c r="K2" t="n">
         <v>55775.116478856</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>171.0636753187676</v>
+        <v>110.954127645421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>55775.116478856</v>
       </c>
       <c r="F3" t="n">
-        <v>166.1834837214486</v>
+        <v>110.954127645421</v>
       </c>
       <c r="G3" t="n">
         <v>55775.116478856</v>
       </c>
       <c r="H3" t="n">
-        <v>173.2135267048389</v>
+        <v>101.7895851530258</v>
       </c>
       <c r="I3" t="n">
         <v>55775.116478856</v>
       </c>
       <c r="J3" t="n">
-        <v>175.8792489774134</v>
+        <v>99.32994800661577</v>
       </c>
       <c r="K3" t="n">
         <v>55775.116478856</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>182.3274958445223</v>
+        <v>127.6046428486035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>55775.116478856</v>
       </c>
       <c r="F4" t="n">
-        <v>183.0162824190104</v>
+        <v>129.9008476214519</v>
       </c>
       <c r="G4" t="n">
         <v>55775.116478856</v>
       </c>
       <c r="H4" t="n">
-        <v>185.1531395705157</v>
+        <v>130.0959625578165</v>
       </c>
       <c r="I4" t="n">
         <v>55775.116478856</v>
       </c>
       <c r="J4" t="n">
-        <v>184.787763663281</v>
+        <v>127.9452205696242</v>
       </c>
       <c r="K4" t="n">
         <v>55775.116478856</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>189.3760976508177</v>
+        <v>151.1904633445999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>55775.116478856</v>
       </c>
       <c r="F5" t="n">
-        <v>190.3449358364332</v>
+        <v>151.231112989809</v>
       </c>
       <c r="G5" t="n">
         <v>55775.116478856</v>
       </c>
       <c r="H5" t="n">
-        <v>191.4167708760838</v>
+        <v>151.0590722498094</v>
       </c>
       <c r="I5" t="n">
         <v>55775.116478856</v>
       </c>
       <c r="J5" t="n">
-        <v>191.0903662499036</v>
+        <v>151.000339316876</v>
       </c>
       <c r="K5" t="n">
         <v>55775.116478856</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>189.3760976508177</v>
+        <v>153.8727345946057</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>55775.116478856</v>
       </c>
       <c r="F6" t="n">
-        <v>190.3449358364332</v>
+        <v>153.6854319963783</v>
       </c>
       <c r="G6" t="n">
         <v>55775.116478856</v>
       </c>
       <c r="H6" t="n">
-        <v>191.4167708760838</v>
+        <v>154.4514900571631</v>
       </c>
       <c r="I6" t="n">
         <v>55775.116478856</v>
       </c>
       <c r="J6" t="n">
-        <v>191.0903662499036</v>
+        <v>154.7130143723211</v>
       </c>
       <c r="K6" t="n">
         <v>55775.116478856</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>83.66267471828399</v>
+        <v>100.2529508426966</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83.66267471828399</v>
+        <v>100.2529508426966</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>48.04195654068081</v>
+        <v>57.56865799088844</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>48.04195654068081</v>
+        <v>57.56865799088844</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>83.66267471828399</v>
+        <v>100.2529508426966</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>83.66267471828399</v>
+        <v>100.2529508426966</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>62.1274857739432</v>
+        <v>74.44734223772392</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>62.1274857739432</v>
+        <v>74.44734223772392</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>83.66267471828399</v>
+        <v>100.2529508426966</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>83.66267471828399</v>
+        <v>100.2529508426966</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>68.40037553035279</v>
+        <v>81.96414361311132</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>68.40037553035279</v>
+        <v>81.96414361311132</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>83.66267471828399</v>
+        <v>100.2529508426966</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>83.66267471828399</v>
+        <v>100.2529508426966</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>71.8377554331642</v>
+        <v>86.0831546247078</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>71.8377554331642</v>
+        <v>86.0831546247078</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>83.66267471828399</v>
+        <v>100.2529508426966</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>83.66267471828399</v>
+        <v>100.2529508426966</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>73.97196651119029</v>
+        <v>88.6405789362512</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>73.97196651119029</v>
+        <v>88.6405789362512</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01673933348941176</v>
+        <v>0.01310034794823529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01673933348941176</v>
+        <v>0.01311917800941176</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01673933348941176</v>
+        <v>0.01311917800941176</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01673933348941176</v>
+        <v>0.01310034794823529</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01746713059764706</v>
+        <v>0.01582914805730055</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01746713059764706</v>
+        <v>0.01591393180444435</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01746713059764706</v>
+        <v>0.01555510312283206</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01746713059764706</v>
+        <v>0.01543260271454518</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01772970725746361</v>
+        <v>0.01582914805730055</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01746713059764706</v>
+        <v>0.01591393180444435</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01789206693816813</v>
+        <v>0.01555510312283206</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01801061317570144</v>
+        <v>0.01543260271454518</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0184575043656989</v>
+        <v>0.01582914805730055</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01819492770588235</v>
+        <v>0.01591393180444434</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01861986404640342</v>
+        <v>0.01555510312283206</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01873841028393673</v>
+        <v>0.01543260271454518</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01915831572470063</v>
+        <v>0.01582914805730055</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01932411166287964</v>
+        <v>0.01591393180444435</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01941558855775854</v>
+        <v>0.01555510312283206</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01918649472751238</v>
+        <v>0.01543260271454518</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1267581153944916</v>
+        <v>0.8588698917263496</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>2.5982356764</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1546568855000003</v>
+        <v>0.8599655584579639</v>
       </c>
       <c r="G18" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="H18" t="n">
-        <v>0.109507399319636</v>
+        <v>0.821167654758621</v>
       </c>
       <c r="I18" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="J18" t="n">
-        <v>0.09691186158172171</v>
+        <v>0.8155633353252988</v>
       </c>
       <c r="K18" t="n">
         <v>2.5982356764</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1267581153944916</v>
+        <v>0.8588698917263496</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>2.5982356764</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1546568855000003</v>
+        <v>0.8599655584579639</v>
       </c>
       <c r="G19" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="H19" t="n">
-        <v>0.109507399319636</v>
+        <v>0.821167654758621</v>
       </c>
       <c r="I19" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09691186158172171</v>
+        <v>0.8155633353252988</v>
       </c>
       <c r="K19" t="n">
         <v>2.5982356764</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1267581153944916</v>
+        <v>0.8588698917263496</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>2.5982356764</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1546568855000003</v>
+        <v>0.8599655584579639</v>
       </c>
       <c r="G20" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="H20" t="n">
-        <v>0.109507399319636</v>
+        <v>0.821167654758621</v>
       </c>
       <c r="I20" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="J20" t="n">
-        <v>0.09691186158172171</v>
+        <v>0.8155633353252988</v>
       </c>
       <c r="K20" t="n">
         <v>2.5982356764</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.05229690850055801</v>
+        <v>0.6756751968652508</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>2.5982356764</v>
       </c>
       <c r="F21" t="n">
-        <v>0.03468109006903821</v>
+        <v>0.6857756582907295</v>
       </c>
       <c r="G21" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02496166998815534</v>
+        <v>0.6316875860054405</v>
       </c>
       <c r="I21" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="J21" t="n">
-        <v>0.04930288945181025</v>
+        <v>0.627074498884473</v>
       </c>
       <c r="K21" t="n">
         <v>2.5982356764</v>
@@ -1477,13 +1477,13 @@
         <v>2.5982356764</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.04849603369909347</v>
       </c>
       <c r="I28" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.0615117020795742</v>
       </c>
       <c r="K28" t="n">
         <v>2.5982356764</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.01937875941181591</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>2.5982356764</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.01037048627778848</v>
       </c>
       <c r="G29" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.04849603369909347</v>
       </c>
       <c r="I29" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.0615117020795742</v>
       </c>
       <c r="K29" t="n">
         <v>2.5982356764</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.01937875941181591</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>2.5982356764</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.01037048627778848</v>
       </c>
       <c r="G30" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.04849603369909347</v>
       </c>
       <c r="I30" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.0615117020795742</v>
       </c>
       <c r="K30" t="n">
         <v>2.5982356764</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.113794976120622</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>2.5982356764</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.1045773685277879</v>
       </c>
       <c r="G31" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.1546568855</v>
       </c>
       <c r="I31" t="n">
         <v>2.5982356764</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.1546568855</v>
       </c>
       <c r="K31" t="n">
         <v>2.5982356764</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>1.622739747904645</v>
+        <v>1.500218326969653</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>17.08978582888011</v>
       </c>
       <c r="F52" t="n">
-        <v>1.367147102033365</v>
+        <v>1.494918815922641</v>
       </c>
       <c r="G52" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="H52" t="n">
-        <v>1.367147102033365</v>
+        <v>1.494918815922642</v>
       </c>
       <c r="I52" t="n">
         <v>4.604510346945146</v>
       </c>
       <c r="J52" t="n">
-        <v>1.622739747904646</v>
+        <v>1.500218326969653</v>
       </c>
       <c r="K52" t="n">
         <v>4.604510346945146</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>4.690542673802406</v>
+        <v>4.738825409212796</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>17.08978582888011</v>
       </c>
       <c r="F53" t="n">
-        <v>4.566392312796181</v>
+        <v>4.737493213186452</v>
       </c>
       <c r="G53" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="H53" t="n">
-        <v>4.584814822704959</v>
+        <v>4.743131441737157</v>
       </c>
       <c r="I53" t="n">
         <v>6.792891173382149</v>
       </c>
       <c r="J53" t="n">
-        <v>4.693689872312135</v>
+        <v>4.745056274769936</v>
       </c>
       <c r="K53" t="n">
         <v>6.792891173382149</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>5.948648258224626</v>
+        <v>5.854529130160984</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>17.08978582888011</v>
       </c>
       <c r="F54" t="n">
-        <v>5.868079710652655</v>
+        <v>5.836233513148303</v>
       </c>
       <c r="G54" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="H54" t="n">
-        <v>5.866316358852814</v>
+        <v>5.842373769326064</v>
       </c>
       <c r="I54" t="n">
         <v>8.047584674651976</v>
       </c>
       <c r="J54" t="n">
-        <v>5.946546701018713</v>
+        <v>5.860416178243643</v>
       </c>
       <c r="K54" t="n">
         <v>8.047584674651976</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>5.831115575687869</v>
+        <v>5.781265396017701</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>17.08978582888011</v>
       </c>
       <c r="F55" t="n">
-        <v>5.74477315236237</v>
+        <v>5.72889990823921</v>
       </c>
       <c r="G55" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="H55" t="n">
-        <v>5.747283587852326</v>
+        <v>5.734905802058422</v>
       </c>
       <c r="I55" t="n">
         <v>8.854862100657989</v>
       </c>
       <c r="J55" t="n">
-        <v>5.829477045914325</v>
+        <v>5.786696097792623</v>
       </c>
       <c r="K55" t="n">
         <v>8.854862100657989</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>5.813658114559425</v>
+        <v>5.726606877611025</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>17.08978582888011</v>
       </c>
       <c r="F56" t="n">
-        <v>5.624368823653654</v>
+        <v>5.433130786630572</v>
       </c>
       <c r="G56" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="H56" t="n">
-        <v>5.624533340361575</v>
+        <v>5.436642154942107</v>
       </c>
       <c r="I56" t="n">
         <v>9.416032088692647</v>
       </c>
       <c r="J56" t="n">
-        <v>5.81439143250963</v>
+        <v>5.731307757809282</v>
       </c>
       <c r="K56" t="n">
         <v>9.416032088692647</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>1.123816895556231</v>
+        <v>0</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>17.08978582888011</v>
       </c>
       <c r="F64" t="n">
-        <v>1.201156756060289</v>
+        <v>0.01827409080809037</v>
       </c>
       <c r="G64" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="H64" t="n">
-        <v>1.19290358996245</v>
+        <v>0.01740189974666808</v>
       </c>
       <c r="I64" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="J64" t="n">
-        <v>1.114385947361713</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
         <v>17.08978582888011</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>2.208309257125979</v>
+        <v>0.8590964282924546</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>17.08978582888011</v>
       </c>
       <c r="F65" t="n">
-        <v>2.290110251456404</v>
+        <v>0.9100111013678549</v>
       </c>
       <c r="G65" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="H65" t="n">
-        <v>2.282575589218087</v>
+        <v>0.9101454637264061</v>
       </c>
       <c r="I65" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="J65" t="n">
-        <v>2.201912152841307</v>
+        <v>0.8604513880752311</v>
       </c>
       <c r="K65" t="n">
         <v>17.08978582888011</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>3.249900123053559</v>
+        <v>1.509247151233464</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>17.08978582888011</v>
       </c>
       <c r="F66" t="n">
-        <v>3.434647984964258</v>
+        <v>1.802279240797569</v>
       </c>
       <c r="G66" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="H66" t="n">
-        <v>3.429459241507974</v>
+        <v>1.800647011451096</v>
       </c>
       <c r="I66" t="n">
         <v>17.08978582888011</v>
       </c>
       <c r="J66" t="n">
-        <v>3.241131171045139</v>
+        <v>1.506622927231242</v>
       </c>
       <c r="K66" t="n">
         <v>17.08978582888011</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.518765186224825</v>
+        <v>17.08978582888011</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.518765186224825</v>
+        <v>17.08978582888011</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.878590838469882</v>
+        <v>17.08978582888011</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.878590838469882</v>
+        <v>17.08978582888011</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1.156647466620295</v>
+        <v>17.08978582888011</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1.156647466620295</v>
+        <v>17.08978582888011</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1.38270792802821</v>
+        <v>17.08978582888011</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1.38270792802821</v>
+        <v>17.08978582888011</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1.572455292983015</v>
+        <v>17.08978582888011</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1.572455292983015</v>
+        <v>17.08978582888011</v>
       </c>
     </row>
     <row r="77">
@@ -3293,13 +3293,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.518765186224825</v>
+        <v>17.08978582888011</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.518765186224825</v>
+        <v>17.08978582888011</v>
       </c>
     </row>
     <row r="78">
@@ -3330,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.878590838469882</v>
+        <v>17.08978582888011</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.878590838469882</v>
+        <v>17.08978582888011</v>
       </c>
     </row>
     <row r="79">
@@ -3367,13 +3367,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1.156647466620295</v>
+        <v>17.08978582888011</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1.156647466620295</v>
+        <v>17.08978582888011</v>
       </c>
     </row>
     <row r="80">
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1.38270792802821</v>
+        <v>17.08978582888011</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1.38270792802821</v>
+        <v>17.08978582888011</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1.572455292983015</v>
+        <v>17.08978582888011</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1.572455292983015</v>
+        <v>17.08978582888011</v>
       </c>
     </row>
     <row r="82">
